--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:49</t>
+    <t xml:space="preserve">2026-09-09 20:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:12</t>
+    <t xml:space="preserve">2026-09-18 17:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_maule.xlsx
@@ -30,96 +30,96 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelluhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualañé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curepto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colbún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Clemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Javier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alegre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maule</t>
   </si>
   <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alegre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Javier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Clemente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colbún</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curepto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pencahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelluhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:06</t>
+    <t xml:space="preserve">2026-09-27 21:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -549,13 +549,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>54006</v>
+        <v>12537</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>66867</v>
+        <v>9331</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>80.77</v>
+        <v>134.36</v>
       </c>
     </row>
     <row r="3">
@@ -563,13 +563,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3884</v>
+        <v>13779</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4185</v>
+        <v>10294</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>92.81</v>
+        <v>133.85</v>
       </c>
     </row>
     <row r="4">
@@ -577,13 +577,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11348</v>
+        <v>10964</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11632</v>
+        <v>8361</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>97.56</v>
+        <v>131.13</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>238894</v>
+        <v>10851</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>241064</v>
+        <v>8625</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>99.1</v>
+        <v>125.81</v>
       </c>
     </row>
     <row r="6">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>51336</v>
+        <v>20267</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>51539</v>
+        <v>16742</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>99.61</v>
+        <v>121.05</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>169955</v>
+        <v>12047</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>169681</v>
+        <v>10230</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>100.16</v>
+        <v>117.76</v>
       </c>
     </row>
     <row r="8">
@@ -633,13 +633,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>31900</v>
+        <v>10713</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>31639</v>
+        <v>9209</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>100.82</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="9">
@@ -647,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>18356</v>
+        <v>37956</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>17913</v>
+        <v>33467</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>102.47</v>
+        <v>113.41</v>
       </c>
     </row>
     <row r="10">
@@ -661,13 +661,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>52460</v>
+        <v>16666</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50985</v>
+        <v>15042</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>102.89</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="11">
@@ -675,13 +675,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>52558</v>
+        <v>50000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>50601</v>
+        <v>45347</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>103.87</v>
+        <v>110.26</v>
       </c>
     </row>
     <row r="12">
@@ -689,13 +689,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>9675</v>
+        <v>4771</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9278</v>
+        <v>4329</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>104.28</v>
+        <v>110.21</v>
       </c>
     </row>
     <row r="13">
@@ -703,13 +703,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>50278</v>
+        <v>7639</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>47590</v>
+        <v>6989</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>105.65</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="14">
@@ -717,13 +717,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>109440</v>
+        <v>21308</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>103303</v>
+        <v>19658</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>105.94</v>
+        <v>108.39</v>
       </c>
     </row>
     <row r="15">
@@ -731,13 +731,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>22771</v>
+        <v>25044</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>21397</v>
+        <v>23262</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>106.42</v>
+        <v>107.66</v>
       </c>
     </row>
     <row r="16">
@@ -745,13 +745,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>21052</v>
+        <v>47667</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>19692</v>
+        <v>44389</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>106.91</v>
+        <v>107.38</v>
       </c>
     </row>
     <row r="17">
@@ -759,13 +759,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>47667</v>
+        <v>21052</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>44389</v>
+        <v>19692</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>107.38</v>
+        <v>106.91</v>
       </c>
     </row>
     <row r="18">
@@ -773,13 +773,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>25044</v>
+        <v>22771</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>23262</v>
+        <v>21397</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>107.66</v>
+        <v>106.42</v>
       </c>
     </row>
     <row r="19">
@@ -787,13 +787,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>21308</v>
+        <v>109440</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>19658</v>
+        <v>103303</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>108.39</v>
+        <v>105.94</v>
       </c>
     </row>
     <row r="20">
@@ -801,13 +801,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7639</v>
+        <v>50278</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6989</v>
+        <v>47590</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>109.3</v>
+        <v>105.65</v>
       </c>
     </row>
     <row r="21">
@@ -815,13 +815,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4771</v>
+        <v>9675</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4329</v>
+        <v>9278</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>110.21</v>
+        <v>104.28</v>
       </c>
     </row>
     <row r="22">
@@ -829,13 +829,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>50000</v>
+        <v>52558</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45347</v>
+        <v>50601</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>110.26</v>
+        <v>103.87</v>
       </c>
     </row>
     <row r="23">
@@ -843,13 +843,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>16666</v>
+        <v>52460</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>15042</v>
+        <v>50985</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>110.8</v>
+        <v>102.89</v>
       </c>
     </row>
     <row r="24">
@@ -857,13 +857,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>37956</v>
+        <v>18356</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>33467</v>
+        <v>17913</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>113.41</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="25">
@@ -871,13 +871,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>10713</v>
+        <v>31900</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9209</v>
+        <v>31639</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>116.33</v>
+        <v>100.82</v>
       </c>
     </row>
     <row r="26">
@@ -885,13 +885,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>12047</v>
+        <v>169955</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10230</v>
+        <v>169681</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>117.76</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="27">
@@ -899,13 +899,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>20267</v>
+        <v>51336</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>16742</v>
+        <v>51539</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>121.05</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="28">
@@ -913,13 +913,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10851</v>
+        <v>238894</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8625</v>
+        <v>241064</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>125.81</v>
+        <v>99.1</v>
       </c>
     </row>
     <row r="29">
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>10964</v>
+        <v>11348</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>8361</v>
+        <v>11632</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>131.13</v>
+        <v>97.56</v>
       </c>
     </row>
     <row r="30">
@@ -941,13 +941,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>13779</v>
+        <v>3884</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>10294</v>
+        <v>4185</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>133.85</v>
+        <v>92.81</v>
       </c>
     </row>
     <row r="31">
@@ -955,13 +955,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>12537</v>
+        <v>54006</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>9331</v>
+        <v>66867</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>134.36</v>
+        <v>80.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:52</t>
+    <t xml:space="preserve">2026-10-05 05:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
